--- a/tools/importer/reports/import-products.report.xlsx
+++ b/tools/importer/reports/import-products.report.xlsx
@@ -40,7 +40,7 @@
     <t>en/products/immunoassay.report.json</t>
   </si>
   <si>
-    <t>["hero","cards-grid","cards-grid","columns","columns","content-reversed","carousel"]</t>
+    <t>["hero","cards-grid","cards-grid","columns","columns","columns","columns","content-reversed","carousel"]</t>
   </si>
   <si>
     <t>en/products/immunoassay</t>
@@ -52,7 +52,7 @@
     <t>products</t>
   </si>
   <si>
-    <t>2026-09-09T13:32:10.017Z</t>
+    <t>2026-09-09T13:52:16.844Z</t>
   </si>
   <si>
     <t>Immunoassay Analyzers and Assays | Beckman Coulter</t>
